--- a/template_importacao_instrumentos.xlsx
+++ b/template_importacao_instrumentos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://odsmetering-my.sharepoint.com/personal/m_bandeira_odsenergysolutions_com/Documents/Documents/AC's_app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_E422F639534ECCEF666EE414525DCE3AB7C07E21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E17D0B7-AF59-4E10-A203-11B54964C60A}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_E422F639534ECCEF666EE414525DCE3AB7C07E21" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{482C8CF4-6908-4650-B2B9-497415BCFB3E}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -606,7 +606,7 @@
     <col min="2" max="2" width="25" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="6" width="12" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="40" customWidth="1"/>
   </cols>
   <sheetData>
